--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Conditional Formatting & Absolute Relative.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Conditional Formatting & Absolute Relative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58AB2EB9-D2C6-468F-9EE5-833D6E6605B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFC12AE-A34B-47F1-8264-F0ECCE641FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A9DA91B2-FB73-4C98-B2C1-A35502413EAF}"/>
   </bookViews>
@@ -1719,7 +1719,10 @@
       <c r="H5" s="5">
         <v>40</v>
       </c>
-      <c r="I5" s="8"/>
+      <c r="I5" s="8">
+        <f>G5*$H$5</f>
+        <v>400</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -1744,7 +1747,10 @@
       <c r="H6" s="4">
         <v>2</v>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="8">
+        <f t="shared" ref="I6:I8" si="1">G6*$H$5</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -1769,7 +1775,10 @@
       <c r="H7" s="4">
         <v>3</v>
       </c>
-      <c r="I7" s="8"/>
+      <c r="I7" s="8">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
@@ -1794,7 +1803,10 @@
       <c r="H8" s="4">
         <v>4</v>
       </c>
-      <c r="I8" s="8"/>
+      <c r="I8" s="8">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Conditional Formatting & Absolute Relative.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Conditional Formatting & Absolute Relative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFC12AE-A34B-47F1-8264-F0ECCE641FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938CBD6B-A94F-4684-BE5B-C89A300BB194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A9DA91B2-FB73-4C98-B2C1-A35502413EAF}"/>
   </bookViews>
